--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624237</v>
+        <v>129624288</v>
       </c>
       <c r="B2" t="n">
-        <v>96102</v>
+        <v>100957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665235</v>
+        <v>665061</v>
       </c>
       <c r="R2" t="n">
-        <v>6703837</v>
+        <v>6703834</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>129624236</v>
       </c>
       <c r="B3" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624239</v>
       </c>
       <c r="B4" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624288</v>
+        <v>129624237</v>
       </c>
       <c r="B5" t="n">
-        <v>100945</v>
+        <v>96114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665061</v>
+        <v>665235</v>
       </c>
       <c r="R5" t="n">
-        <v>6703834</v>
+        <v>6703837</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>91354</v>
+        <v>100957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B8" t="n">
-        <v>100945</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>98734</v>
+        <v>100957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R9" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>100945</v>
+        <v>98746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R10" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1673,7 +1673,7 @@
         <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B14" t="n">
-        <v>96102</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,34 +1875,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R14" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1950,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>96114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,39 +1992,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2047,21 +2062,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2081,7 +2081,7 @@
         <v>129624252</v>
       </c>
       <c r="B16" t="n">
-        <v>98734</v>
+        <v>98746</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129624231</v>
       </c>
       <c r="B17" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,34 +2272,30 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B18" t="n">
-        <v>96102</v>
+        <v>91607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R18" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2353,6 +2349,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2372,7 +2383,7 @@
         <v>129624286</v>
       </c>
       <c r="B19" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,30 +2477,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624274</v>
+        <v>129624238</v>
       </c>
       <c r="B20" t="n">
-        <v>91601</v>
+        <v>96114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2497,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665304</v>
+        <v>665241</v>
       </c>
       <c r="R20" t="n">
-        <v>6703880</v>
+        <v>6703839</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2543,21 +2558,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2577,7 +2577,7 @@
         <v>129624291</v>
       </c>
       <c r="B21" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624272</v>
       </c>
       <c r="B22" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>96198</v>
+        <v>100957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R23" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>100945</v>
+        <v>96210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R24" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624268</v>
+        <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>75182</v>
+        <v>92542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665254</v>
+        <v>665217</v>
       </c>
       <c r="R25" t="n">
-        <v>6703848</v>
+        <v>6703818</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,21 +3043,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3074,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>92536</v>
+        <v>75187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3085,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3109,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R26" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3155,6 +3140,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624224</v>
+        <v>129624240</v>
       </c>
       <c r="B27" t="n">
-        <v>97002</v>
+        <v>96114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665142</v>
+        <v>665198</v>
       </c>
       <c r="R27" t="n">
-        <v>6703804</v>
+        <v>6703801</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,21 +3252,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3283,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624240</v>
+        <v>129624216</v>
       </c>
       <c r="B28" t="n">
-        <v>96102</v>
+        <v>101864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3318,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665198</v>
+        <v>665152</v>
       </c>
       <c r="R28" t="n">
-        <v>6703801</v>
+        <v>6703982</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3380,32 +3365,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624290</v>
+        <v>129624224</v>
       </c>
       <c r="B29" t="n">
-        <v>100945</v>
+        <v>97014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665221</v>
+        <v>665142</v>
       </c>
       <c r="R29" t="n">
-        <v>6703828</v>
+        <v>6703804</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,6 +3446,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624216</v>
+        <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>101852</v>
+        <v>100957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665152</v>
+        <v>665221</v>
       </c>
       <c r="R30" t="n">
-        <v>6703982</v>
+        <v>6703828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3577,7 +3577,7 @@
         <v>129624267</v>
       </c>
       <c r="B31" t="n">
-        <v>75182</v>
+        <v>75187</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624288</v>
       </c>
       <c r="B2" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624236</v>
       </c>
       <c r="B3" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624239</v>
       </c>
       <c r="B4" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624237</v>
       </c>
       <c r="B5" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B6" t="n">
-        <v>100957</v>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>91360</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,7 +1362,7 @@
         <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>98747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1639,21 +1634,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1670,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B12" t="n">
-        <v>98746</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,34 +1661,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R12" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1751,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129624234</v>
       </c>
       <c r="B15" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>98746</v>
+        <v>96115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>96114</v>
+        <v>98747</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2275,7 +2275,7 @@
         <v>129624274</v>
       </c>
       <c r="B18" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129624286</v>
       </c>
       <c r="B19" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129624238</v>
       </c>
       <c r="B20" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624291</v>
+        <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>100957</v>
+        <v>96211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665217</v>
+        <v>665227</v>
       </c>
       <c r="R21" t="n">
-        <v>6703817</v>
+        <v>6703829</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624272</v>
+        <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>96210</v>
+        <v>100958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665227</v>
+        <v>665217</v>
       </c>
       <c r="R22" t="n">
-        <v>6703829</v>
+        <v>6703817</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2771,7 +2771,7 @@
         <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>129624240</v>
       </c>
       <c r="B27" t="n">
-        <v>96114</v>
+        <v>96115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624216</v>
+        <v>129624224</v>
       </c>
       <c r="B28" t="n">
-        <v>101864</v>
+        <v>97015</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665152</v>
+        <v>665142</v>
       </c>
       <c r="R28" t="n">
-        <v>6703982</v>
+        <v>6703804</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,6 +3349,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3365,32 +3380,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624224</v>
+        <v>129624216</v>
       </c>
       <c r="B29" t="n">
-        <v>97014</v>
+        <v>101865</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3400,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665142</v>
+        <v>665152</v>
       </c>
       <c r="R29" t="n">
-        <v>6703804</v>
+        <v>6703982</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3446,21 +3461,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3480,7 +3480,7 @@
         <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>129624267</v>
       </c>
       <c r="B31" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B32" t="n">
-        <v>100957</v>
+        <v>91552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,6 +3744,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3752,6 +3757,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3768,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>91551</v>
+        <v>100958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3861,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>96115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,39 +1875,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1950,21 +1945,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1981,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B15" t="n">
-        <v>96115</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,34 +1972,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R15" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,6 +2047,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B16" t="n">
-        <v>96115</v>
+        <v>98747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B17" t="n">
-        <v>98747</v>
+        <v>96115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2272,30 +2272,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624274</v>
+        <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>91608</v>
+        <v>96115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2303,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665304</v>
+        <v>665241</v>
       </c>
       <c r="R18" t="n">
-        <v>6703880</v>
+        <v>6703839</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2349,21 +2353,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2380,34 +2369,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624286</v>
+        <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>100958</v>
+        <v>91608</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2415,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665264</v>
+        <v>665304</v>
       </c>
       <c r="R19" t="n">
-        <v>6703843</v>
+        <v>6703880</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2461,6 +2446,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624238</v>
+        <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>96115</v>
+        <v>100958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665241</v>
+        <v>665264</v>
       </c>
       <c r="R20" t="n">
-        <v>6703839</v>
+        <v>6703843</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B25" t="n">
-        <v>92543</v>
+        <v>75188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R25" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,6 +3043,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3059,10 +3074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624268</v>
+        <v>129624230</v>
       </c>
       <c r="B26" t="n">
-        <v>75188</v>
+        <v>92543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,21 +3085,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665254</v>
+        <v>665217</v>
       </c>
       <c r="R26" t="n">
-        <v>6703848</v>
+        <v>6703818</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3140,21 +3155,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>91552</v>
+        <v>100958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R32" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,11 +3744,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3752,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3788,10 +3768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>100958</v>
+        <v>91552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3779,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3803,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R33" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3861,6 +3841,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3869,6 +3854,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624288</v>
+        <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>100958</v>
+        <v>96120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665061</v>
+        <v>665196</v>
       </c>
       <c r="R2" t="n">
-        <v>6703834</v>
+        <v>6703839</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624236</v>
+        <v>129624239</v>
       </c>
       <c r="B3" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665196</v>
+        <v>665227</v>
       </c>
       <c r="R3" t="n">
-        <v>6703839</v>
+        <v>6703829</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624239</v>
+        <v>129624237</v>
       </c>
       <c r="B4" t="n">
-        <v>96115</v>
+        <v>96120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665227</v>
+        <v>665235</v>
       </c>
       <c r="R4" t="n">
-        <v>6703829</v>
+        <v>6703837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624237</v>
+        <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>96115</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665235</v>
+        <v>665061</v>
       </c>
       <c r="R5" t="n">
-        <v>6703837</v>
+        <v>6703834</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,45 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624229</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665157</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703792</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>100963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R7" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>91366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,7 +1362,7 @@
         <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B11" t="n">
-        <v>98747</v>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1564,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R11" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1634,6 +1639,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1650,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>98752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,39 +1681,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R12" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1751,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B14" t="n">
-        <v>96115</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,34 +1875,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R14" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1950,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>96120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,39 +1992,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2047,21 +2062,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>98747</v>
+        <v>96120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>96115</v>
+        <v>98752</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2272,34 +2272,30 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B18" t="n">
-        <v>96115</v>
+        <v>91613</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R18" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2353,6 +2349,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2369,30 +2380,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624274</v>
+        <v>129624286</v>
       </c>
       <c r="B19" t="n">
-        <v>91608</v>
+        <v>100963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2400,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665304</v>
+        <v>665264</v>
       </c>
       <c r="R19" t="n">
-        <v>6703880</v>
+        <v>6703843</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2446,21 +2461,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B20" t="n">
-        <v>100958</v>
+        <v>96120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R20" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624272</v>
+        <v>129624291</v>
       </c>
       <c r="B21" t="n">
-        <v>96211</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665227</v>
+        <v>665217</v>
       </c>
       <c r="R21" t="n">
-        <v>6703829</v>
+        <v>6703817</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624291</v>
+        <v>129624272</v>
       </c>
       <c r="B22" t="n">
-        <v>100958</v>
+        <v>96216</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665217</v>
+        <v>665227</v>
       </c>
       <c r="R22" t="n">
-        <v>6703817</v>
+        <v>6703829</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2771,7 +2771,7 @@
         <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624268</v>
+        <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>75188</v>
+        <v>92548</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665254</v>
+        <v>665217</v>
       </c>
       <c r="R25" t="n">
-        <v>6703848</v>
+        <v>6703818</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,21 +3043,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3074,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>92543</v>
+        <v>75193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3085,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3109,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R26" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3155,6 +3140,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624240</v>
+        <v>129624290</v>
       </c>
       <c r="B27" t="n">
-        <v>96115</v>
+        <v>100963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665198</v>
+        <v>665221</v>
       </c>
       <c r="R27" t="n">
-        <v>6703801</v>
+        <v>6703828</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624224</v>
+        <v>129624216</v>
       </c>
       <c r="B28" t="n">
-        <v>97015</v>
+        <v>101870</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665142</v>
+        <v>665152</v>
       </c>
       <c r="R28" t="n">
-        <v>6703804</v>
+        <v>6703982</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,21 +3349,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,32 +3365,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624216</v>
+        <v>129624224</v>
       </c>
       <c r="B29" t="n">
-        <v>101865</v>
+        <v>97020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665152</v>
+        <v>665142</v>
       </c>
       <c r="R29" t="n">
-        <v>6703982</v>
+        <v>6703804</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,6 +3446,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624290</v>
+        <v>129624240</v>
       </c>
       <c r="B30" t="n">
-        <v>100958</v>
+        <v>96120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665221</v>
+        <v>665198</v>
       </c>
       <c r="R30" t="n">
-        <v>6703828</v>
+        <v>6703801</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3577,7 +3577,7 @@
         <v>129624267</v>
       </c>
       <c r="B31" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B32" t="n">
-        <v>100958</v>
+        <v>91557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,6 +3744,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3752,6 +3757,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3768,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>91552</v>
+        <v>100963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3861,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624229</v>
+        <v>129624258</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>91366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665157</v>
+        <v>665281</v>
       </c>
       <c r="R6" t="n">
-        <v>6703792</v>
+        <v>6703851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>100963</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R7" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>91366</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1639,21 +1634,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1670,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B12" t="n">
-        <v>98752</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,34 +1661,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R12" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1751,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>96120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,39 +1875,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1950,21 +1945,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1981,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B15" t="n">
-        <v>96120</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,34 +1972,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R15" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,6 +2047,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B16" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B17" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B19" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,21 +2391,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R19" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624238</v>
+        <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665241</v>
+        <v>665264</v>
       </c>
       <c r="R20" t="n">
-        <v>6703839</v>
+        <v>6703843</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624291</v>
+        <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>96216</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665217</v>
+        <v>665227</v>
       </c>
       <c r="R21" t="n">
-        <v>6703817</v>
+        <v>6703829</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624272</v>
+        <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>96216</v>
+        <v>100963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665227</v>
+        <v>665217</v>
       </c>
       <c r="R22" t="n">
-        <v>6703829</v>
+        <v>6703817</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624290</v>
+        <v>129624240</v>
       </c>
       <c r="B27" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665221</v>
+        <v>665198</v>
       </c>
       <c r="R27" t="n">
-        <v>6703828</v>
+        <v>6703801</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624216</v>
+        <v>129624224</v>
       </c>
       <c r="B28" t="n">
-        <v>101870</v>
+        <v>97020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665152</v>
+        <v>665142</v>
       </c>
       <c r="R28" t="n">
-        <v>6703982</v>
+        <v>6703804</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,6 +3349,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3365,32 +3380,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624224</v>
+        <v>129624216</v>
       </c>
       <c r="B29" t="n">
-        <v>97020</v>
+        <v>101870</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3400,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665142</v>
+        <v>665152</v>
       </c>
       <c r="R29" t="n">
-        <v>6703804</v>
+        <v>6703982</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3446,21 +3461,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624240</v>
+        <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665198</v>
+        <v>665221</v>
       </c>
       <c r="R30" t="n">
-        <v>6703801</v>
+        <v>6703828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>100963</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R32" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,11 +3744,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3752,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3788,10 +3768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>100963</v>
+        <v>91557</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3779,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3803,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R33" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3861,6 +3841,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3869,6 +3854,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624236</v>
+        <v>129624288</v>
       </c>
       <c r="B2" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665196</v>
+        <v>665061</v>
       </c>
       <c r="R2" t="n">
-        <v>6703839</v>
+        <v>6703834</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624239</v>
+        <v>129624236</v>
       </c>
       <c r="B3" t="n">
         <v>96120</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665227</v>
+        <v>665196</v>
       </c>
       <c r="R3" t="n">
-        <v>6703829</v>
+        <v>6703839</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624237</v>
+        <v>129624239</v>
       </c>
       <c r="B4" t="n">
         <v>96120</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665235</v>
+        <v>665227</v>
       </c>
       <c r="R4" t="n">
-        <v>6703837</v>
+        <v>6703829</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624288</v>
+        <v>129624237</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665061</v>
+        <v>665235</v>
       </c>
       <c r="R5" t="n">
-        <v>6703834</v>
+        <v>6703837</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>98752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R9" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B10" t="n">
-        <v>98752</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R10" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1564,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R11" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1634,6 +1639,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1650,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>98752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,39 +1681,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R12" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1751,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B14" t="n">
-        <v>96120</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,34 +1875,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R14" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1945,6 +1950,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1961,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>96120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,39 +1992,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R15" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2047,21 +2062,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>98752</v>
+        <v>96120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>96120</v>
+        <v>98752</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2272,30 +2272,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624274</v>
+        <v>129624286</v>
       </c>
       <c r="B18" t="n">
-        <v>91613</v>
+        <v>100963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2303,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665304</v>
+        <v>665264</v>
       </c>
       <c r="R18" t="n">
-        <v>6703880</v>
+        <v>6703843</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2349,21 +2353,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2380,34 +2369,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>96120</v>
+        <v>91613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2415,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R19" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2461,6 +2446,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R20" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>100963</v>
+        <v>96216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R23" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>96216</v>
+        <v>100963</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R24" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B27" t="n">
-        <v>96120</v>
+        <v>97020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R27" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,6 +3252,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3268,32 +3283,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624224</v>
+        <v>129624240</v>
       </c>
       <c r="B28" t="n">
-        <v>97020</v>
+        <v>96120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665142</v>
+        <v>665198</v>
       </c>
       <c r="R28" t="n">
-        <v>6703804</v>
+        <v>6703801</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,21 +3364,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,10 +3380,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624216</v>
+        <v>129624290</v>
       </c>
       <c r="B29" t="n">
-        <v>101870</v>
+        <v>100963</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,21 +3391,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665152</v>
+        <v>665221</v>
       </c>
       <c r="R29" t="n">
-        <v>6703982</v>
+        <v>6703828</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624290</v>
+        <v>129624216</v>
       </c>
       <c r="B30" t="n">
-        <v>100963</v>
+        <v>101870</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665221</v>
+        <v>665152</v>
       </c>
       <c r="R30" t="n">
-        <v>6703828</v>
+        <v>6703982</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624288</v>
+        <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665061</v>
+        <v>665196</v>
       </c>
       <c r="R2" t="n">
-        <v>6703834</v>
+        <v>6703839</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624236</v>
+        <v>129624239</v>
       </c>
       <c r="B3" t="n">
         <v>96120</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665196</v>
+        <v>665227</v>
       </c>
       <c r="R3" t="n">
-        <v>6703839</v>
+        <v>6703829</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624239</v>
+        <v>129624237</v>
       </c>
       <c r="B4" t="n">
         <v>96120</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665227</v>
+        <v>665235</v>
       </c>
       <c r="R4" t="n">
-        <v>6703829</v>
+        <v>6703837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624237</v>
+        <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665235</v>
+        <v>665061</v>
       </c>
       <c r="R5" t="n">
-        <v>6703837</v>
+        <v>6703834</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,45 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624229</v>
       </c>
       <c r="B6" t="n">
-        <v>91366</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665157</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703792</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624229</v>
+        <v>129624258</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>91366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665157</v>
+        <v>665281</v>
       </c>
       <c r="R7" t="n">
-        <v>6703792</v>
+        <v>6703851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624282</v>
+        <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>96120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,39 +1875,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665066</v>
+        <v>665142</v>
       </c>
       <c r="R14" t="n">
-        <v>6703824</v>
+        <v>6703802</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1950,21 +1945,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1981,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624234</v>
+        <v>129624282</v>
       </c>
       <c r="B15" t="n">
-        <v>96120</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,34 +1972,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665142</v>
+        <v>665066</v>
       </c>
       <c r="R15" t="n">
-        <v>6703802</v>
+        <v>6703824</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2062,6 +2047,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R18" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624238</v>
+        <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665241</v>
+        <v>665264</v>
       </c>
       <c r="R20" t="n">
-        <v>6703839</v>
+        <v>6703843</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>96216</v>
+        <v>100963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R23" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>100963</v>
+        <v>96216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R24" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624224</v>
+        <v>129624216</v>
       </c>
       <c r="B27" t="n">
-        <v>97020</v>
+        <v>101870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665142</v>
+        <v>665152</v>
       </c>
       <c r="R27" t="n">
-        <v>6703804</v>
+        <v>6703982</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,21 +3252,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3283,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624240</v>
+        <v>129624290</v>
       </c>
       <c r="B28" t="n">
-        <v>96120</v>
+        <v>100963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3318,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665198</v>
+        <v>665221</v>
       </c>
       <c r="R28" t="n">
-        <v>6703801</v>
+        <v>6703828</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3380,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624290</v>
+        <v>129624240</v>
       </c>
       <c r="B29" t="n">
-        <v>100963</v>
+        <v>96120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,21 +3376,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665221</v>
+        <v>665198</v>
       </c>
       <c r="R29" t="n">
-        <v>6703828</v>
+        <v>6703801</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624216</v>
+        <v>129624224</v>
       </c>
       <c r="B30" t="n">
-        <v>101870</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665152</v>
+        <v>665142</v>
       </c>
       <c r="R30" t="n">
-        <v>6703982</v>
+        <v>6703804</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,6 +3543,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624239</v>
       </c>
       <c r="B3" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624237</v>
       </c>
       <c r="B4" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>100967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,7 +1163,7 @@
         <v>129624258</v>
       </c>
       <c r="B7" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>98752</v>
+        <v>100967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R9" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R10" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1673,7 +1673,7 @@
         <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>96120</v>
+        <v>96124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>100963</v>
+        <v>96220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R23" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>96216</v>
+        <v>100967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R24" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2965,7 +2965,7 @@
         <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624216</v>
+        <v>129624240</v>
       </c>
       <c r="B27" t="n">
-        <v>101870</v>
+        <v>96124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665152</v>
+        <v>665198</v>
       </c>
       <c r="R27" t="n">
-        <v>6703982</v>
+        <v>6703801</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624290</v>
+        <v>129624216</v>
       </c>
       <c r="B28" t="n">
-        <v>100963</v>
+        <v>101874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665221</v>
+        <v>665152</v>
       </c>
       <c r="R28" t="n">
-        <v>6703828</v>
+        <v>6703982</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3365,32 +3365,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B29" t="n">
-        <v>96120</v>
+        <v>97024</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R29" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3446,6 +3446,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3462,32 +3477,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624224</v>
+        <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>100967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665142</v>
+        <v>665221</v>
       </c>
       <c r="R30" t="n">
-        <v>6703804</v>
+        <v>6703828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3543,21 +3558,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B32" t="n">
-        <v>100963</v>
+        <v>91561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,6 +3744,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3752,6 +3757,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3768,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>91557</v>
+        <v>100967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3861,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624239</v>
       </c>
       <c r="B3" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624237</v>
       </c>
       <c r="B4" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B6" t="n">
-        <v>100967</v>
+        <v>91372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624258</v>
+        <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665281</v>
+        <v>665157</v>
       </c>
       <c r="R7" t="n">
-        <v>6703851</v>
+        <v>6703792</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,50 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B9" t="n">
-        <v>100967</v>
+        <v>98758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R9" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>100969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R10" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1673,7 +1673,7 @@
         <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>96124</v>
+        <v>96126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,34 +2272,30 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B18" t="n">
-        <v>96124</v>
+        <v>91619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2307,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R18" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2353,6 +2349,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2369,30 +2380,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624274</v>
+        <v>129624238</v>
       </c>
       <c r="B19" t="n">
-        <v>91617</v>
+        <v>96126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2400,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665304</v>
+        <v>665241</v>
       </c>
       <c r="R19" t="n">
-        <v>6703880</v>
+        <v>6703839</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2446,21 +2461,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2480,7 +2480,7 @@
         <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B25" t="n">
-        <v>92552</v>
+        <v>75193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R25" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,6 +3043,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3059,10 +3074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624268</v>
+        <v>129624230</v>
       </c>
       <c r="B26" t="n">
-        <v>75193</v>
+        <v>92554</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,21 +3085,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665254</v>
+        <v>665217</v>
       </c>
       <c r="R26" t="n">
-        <v>6703848</v>
+        <v>6703818</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3140,21 +3155,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B27" t="n">
-        <v>96124</v>
+        <v>97026</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R27" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,6 +3252,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3268,10 +3283,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624216</v>
+        <v>129624240</v>
       </c>
       <c r="B28" t="n">
-        <v>101874</v>
+        <v>96126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,21 +3294,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665152</v>
+        <v>665198</v>
       </c>
       <c r="R28" t="n">
-        <v>6703982</v>
+        <v>6703801</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3365,32 +3380,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624224</v>
+        <v>129624290</v>
       </c>
       <c r="B29" t="n">
-        <v>97024</v>
+        <v>100969</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3400,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665142</v>
+        <v>665221</v>
       </c>
       <c r="R29" t="n">
-        <v>6703804</v>
+        <v>6703828</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3446,21 +3461,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624290</v>
+        <v>129624216</v>
       </c>
       <c r="B30" t="n">
-        <v>100967</v>
+        <v>101876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665221</v>
+        <v>665152</v>
       </c>
       <c r="R30" t="n">
-        <v>6703828</v>
+        <v>6703982</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>91561</v>
+        <v>100969</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R32" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,11 +3744,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3752,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3788,10 +3768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>100967</v>
+        <v>91563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3779,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3803,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R33" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3861,6 +3841,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3869,6 +3854,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>91372</v>
+        <v>100969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624229</v>
+        <v>129624258</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665157</v>
+        <v>665281</v>
       </c>
       <c r="R7" t="n">
-        <v>6703792</v>
+        <v>6703851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2272,30 +2272,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624274</v>
+        <v>129624286</v>
       </c>
       <c r="B18" t="n">
-        <v>91619</v>
+        <v>100969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2303,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665304</v>
+        <v>665264</v>
       </c>
       <c r="R18" t="n">
-        <v>6703880</v>
+        <v>6703843</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2349,21 +2353,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2477,34 +2466,30 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624286</v>
+        <v>129624274</v>
       </c>
       <c r="B20" t="n">
-        <v>100969</v>
+        <v>91619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2512,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665264</v>
+        <v>665304</v>
       </c>
       <c r="R20" t="n">
-        <v>6703843</v>
+        <v>6703880</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2558,6 +2543,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624272</v>
+        <v>129624291</v>
       </c>
       <c r="B21" t="n">
-        <v>96222</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665227</v>
+        <v>665217</v>
       </c>
       <c r="R21" t="n">
-        <v>6703829</v>
+        <v>6703817</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624291</v>
+        <v>129624272</v>
       </c>
       <c r="B22" t="n">
-        <v>100969</v>
+        <v>96222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665217</v>
+        <v>665227</v>
       </c>
       <c r="R22" t="n">
-        <v>6703817</v>
+        <v>6703829</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>96222</v>
+        <v>100969</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R23" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>100969</v>
+        <v>96222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R24" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B6" t="n">
-        <v>100969</v>
+        <v>91372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624258</v>
+        <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665281</v>
+        <v>665157</v>
       </c>
       <c r="R7" t="n">
-        <v>6703851</v>
+        <v>6703792</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,50 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624291</v>
+        <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>96222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665217</v>
+        <v>665227</v>
       </c>
       <c r="R21" t="n">
-        <v>6703817</v>
+        <v>6703829</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624272</v>
+        <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>96222</v>
+        <v>100969</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665227</v>
+        <v>665217</v>
       </c>
       <c r="R22" t="n">
-        <v>6703829</v>
+        <v>6703817</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B32" t="n">
-        <v>100969</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,6 +3744,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3752,6 +3757,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3768,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>91563</v>
+        <v>100969</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3861,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624236</v>
+        <v>129624288</v>
       </c>
       <c r="B2" t="n">
-        <v>96126</v>
+        <v>100979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665196</v>
+        <v>665061</v>
       </c>
       <c r="R2" t="n">
-        <v>6703839</v>
+        <v>6703834</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624239</v>
+        <v>129624236</v>
       </c>
       <c r="B3" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665227</v>
+        <v>665196</v>
       </c>
       <c r="R3" t="n">
-        <v>6703829</v>
+        <v>6703839</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624237</v>
+        <v>129624239</v>
       </c>
       <c r="B4" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665235</v>
+        <v>665227</v>
       </c>
       <c r="R4" t="n">
-        <v>6703837</v>
+        <v>6703829</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624288</v>
+        <v>129624237</v>
       </c>
       <c r="B5" t="n">
-        <v>100969</v>
+        <v>96136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665061</v>
+        <v>665235</v>
       </c>
       <c r="R5" t="n">
-        <v>6703834</v>
+        <v>6703837</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>91372</v>
+        <v>100979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624229</v>
+        <v>129624258</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665157</v>
+        <v>665281</v>
       </c>
       <c r="R7" t="n">
-        <v>6703792</v>
+        <v>6703851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>98758</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R9" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>100969</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R10" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1639,21 +1634,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1670,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B12" t="n">
-        <v>98758</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,34 +1661,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R12" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1751,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>129624286</v>
       </c>
       <c r="B18" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129624238</v>
       </c>
       <c r="B19" t="n">
-        <v>96126</v>
+        <v>96136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>100969</v>
+        <v>96232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R23" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>96222</v>
+        <v>100979</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R24" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624268</v>
+        <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>75193</v>
+        <v>92554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665254</v>
+        <v>665217</v>
       </c>
       <c r="R25" t="n">
-        <v>6703848</v>
+        <v>6703818</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,21 +3043,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3074,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>92554</v>
+        <v>75193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3085,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3109,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R26" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3155,6 +3140,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624224</v>
+        <v>129624240</v>
       </c>
       <c r="B27" t="n">
-        <v>97026</v>
+        <v>96136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665142</v>
+        <v>665198</v>
       </c>
       <c r="R27" t="n">
-        <v>6703804</v>
+        <v>6703801</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,21 +3252,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3283,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B28" t="n">
-        <v>96126</v>
+        <v>97036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3318,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R28" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3364,6 +3349,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>129624290</v>
       </c>
       <c r="B29" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>129624216</v>
       </c>
       <c r="B30" t="n">
-        <v>101876</v>
+        <v>101886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>100979</v>
+        <v>96136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R18" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2369,34 +2369,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>96136</v>
+        <v>91619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2404,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R19" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2450,6 +2446,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2466,30 +2477,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624274</v>
+        <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>91619</v>
+        <v>100979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2497,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665304</v>
+        <v>665264</v>
       </c>
       <c r="R20" t="n">
-        <v>6703880</v>
+        <v>6703843</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2543,21 +2558,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B27" t="n">
-        <v>96136</v>
+        <v>97036</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R27" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,6 +3252,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3268,32 +3283,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624224</v>
+        <v>129624290</v>
       </c>
       <c r="B28" t="n">
-        <v>97036</v>
+        <v>100979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665142</v>
+        <v>665221</v>
       </c>
       <c r="R28" t="n">
-        <v>6703804</v>
+        <v>6703828</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,21 +3364,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,10 +3380,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624290</v>
+        <v>129624216</v>
       </c>
       <c r="B29" t="n">
-        <v>100979</v>
+        <v>101886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,21 +3391,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665221</v>
+        <v>665152</v>
       </c>
       <c r="R29" t="n">
-        <v>6703828</v>
+        <v>6703982</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624216</v>
+        <v>129624240</v>
       </c>
       <c r="B30" t="n">
-        <v>101886</v>
+        <v>96136</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665152</v>
+        <v>665198</v>
       </c>
       <c r="R30" t="n">
-        <v>6703982</v>
+        <v>6703801</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624238</v>
+        <v>129624286</v>
       </c>
       <c r="B18" t="n">
-        <v>96136</v>
+        <v>100979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665241</v>
+        <v>665264</v>
       </c>
       <c r="R18" t="n">
-        <v>6703839</v>
+        <v>6703843</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2369,30 +2369,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624274</v>
+        <v>129624238</v>
       </c>
       <c r="B19" t="n">
-        <v>91619</v>
+        <v>96136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2400,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665304</v>
+        <v>665241</v>
       </c>
       <c r="R19" t="n">
-        <v>6703880</v>
+        <v>6703839</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2446,21 +2450,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2477,34 +2466,30 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624286</v>
+        <v>129624274</v>
       </c>
       <c r="B20" t="n">
-        <v>100979</v>
+        <v>91619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2512,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665264</v>
+        <v>665304</v>
       </c>
       <c r="R20" t="n">
-        <v>6703843</v>
+        <v>6703880</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2558,6 +2543,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3283,10 +3283,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624290</v>
+        <v>129624240</v>
       </c>
       <c r="B28" t="n">
-        <v>100979</v>
+        <v>96136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,21 +3294,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665221</v>
+        <v>665198</v>
       </c>
       <c r="R28" t="n">
-        <v>6703828</v>
+        <v>6703801</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624240</v>
+        <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>96136</v>
+        <v>100979</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665198</v>
+        <v>665221</v>
       </c>
       <c r="R30" t="n">
-        <v>6703801</v>
+        <v>6703828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624288</v>
+        <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>100979</v>
+        <v>96140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665061</v>
+        <v>665196</v>
       </c>
       <c r="R2" t="n">
-        <v>6703834</v>
+        <v>6703839</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624236</v>
+        <v>129624239</v>
       </c>
       <c r="B3" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665196</v>
+        <v>665227</v>
       </c>
       <c r="R3" t="n">
-        <v>6703839</v>
+        <v>6703829</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624239</v>
+        <v>129624237</v>
       </c>
       <c r="B4" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665227</v>
+        <v>665235</v>
       </c>
       <c r="R4" t="n">
-        <v>6703829</v>
+        <v>6703837</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624237</v>
+        <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>96136</v>
+        <v>100983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665235</v>
+        <v>665061</v>
       </c>
       <c r="R5" t="n">
-        <v>6703837</v>
+        <v>6703834</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624258</v>
       </c>
       <c r="B6" t="n">
-        <v>100979</v>
+        <v>91375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665281</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,45 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624258</v>
+        <v>129624229</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665281</v>
+        <v>665157</v>
       </c>
       <c r="R7" t="n">
-        <v>6703851</v>
+        <v>6703792</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,50 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>100983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,7 +1362,7 @@
         <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1564,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R11" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1634,6 +1639,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1650,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>98772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,39 +1681,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R12" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1751,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B16" t="n">
-        <v>96136</v>
+        <v>98772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>96140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624286</v>
+        <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>100979</v>
+        <v>96140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,21 +2283,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665264</v>
+        <v>665241</v>
       </c>
       <c r="R18" t="n">
-        <v>6703843</v>
+        <v>6703839</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2369,34 +2369,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624238</v>
+        <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>96136</v>
+        <v>91622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2404,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665241</v>
+        <v>665304</v>
       </c>
       <c r="R19" t="n">
-        <v>6703839</v>
+        <v>6703880</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2450,6 +2446,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2466,30 +2477,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624274</v>
+        <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>91619</v>
+        <v>100983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2497,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665304</v>
+        <v>665264</v>
       </c>
       <c r="R20" t="n">
-        <v>6703880</v>
+        <v>6703843</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2543,21 +2558,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2577,7 +2577,7 @@
         <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B23" t="n">
-        <v>96232</v>
+        <v>100983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R23" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B24" t="n">
-        <v>100979</v>
+        <v>96236</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R24" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2965,7 +2965,7 @@
         <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>129624224</v>
       </c>
       <c r="B27" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>129624240</v>
       </c>
       <c r="B28" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>129624216</v>
       </c>
       <c r="B29" t="n">
-        <v>101886</v>
+        <v>101890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>129624267</v>
       </c>
       <c r="B31" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>100983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R32" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,11 +3744,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3752,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3788,10 +3768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>100979</v>
+        <v>91566</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3779,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3803,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R33" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3861,6 +3841,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3869,6 +3854,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624281</v>
+        <v>129624253</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>98772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665191</v>
+        <v>665178</v>
       </c>
       <c r="R11" t="n">
-        <v>6703989</v>
+        <v>6703813</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1639,21 +1634,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1670,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624253</v>
+        <v>129624281</v>
       </c>
       <c r="B12" t="n">
-        <v>98772</v>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,34 +1661,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665178</v>
+        <v>665191</v>
       </c>
       <c r="R12" t="n">
-        <v>6703813</v>
+        <v>6703989</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1751,6 +1736,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624252</v>
+        <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>98772</v>
+        <v>96140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665269</v>
+        <v>665273</v>
       </c>
       <c r="R16" t="n">
         <v>6703827</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624231</v>
+        <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>96140</v>
+        <v>98772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665273</v>
+        <v>665269</v>
       </c>
       <c r="R17" t="n">
         <v>6703827</v>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624289</v>
+        <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>100983</v>
+        <v>96236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2779,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665153</v>
+        <v>665238</v>
       </c>
       <c r="R23" t="n">
-        <v>6703824</v>
+        <v>6703837</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624271</v>
+        <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>96236</v>
+        <v>100983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665238</v>
+        <v>665153</v>
       </c>
       <c r="R24" t="n">
-        <v>6703837</v>
+        <v>6703824</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624224</v>
+        <v>129624290</v>
       </c>
       <c r="B27" t="n">
-        <v>97040</v>
+        <v>100983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665142</v>
+        <v>665221</v>
       </c>
       <c r="R27" t="n">
-        <v>6703804</v>
+        <v>6703828</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,21 +3252,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3283,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624240</v>
+        <v>129624224</v>
       </c>
       <c r="B28" t="n">
-        <v>96140</v>
+        <v>97040</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3318,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665198</v>
+        <v>665142</v>
       </c>
       <c r="R28" t="n">
-        <v>6703801</v>
+        <v>6703804</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3364,6 +3349,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,10 +3380,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624216</v>
+        <v>129624240</v>
       </c>
       <c r="B29" t="n">
-        <v>101890</v>
+        <v>96140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,21 +3391,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665152</v>
+        <v>665198</v>
       </c>
       <c r="R29" t="n">
-        <v>6703982</v>
+        <v>6703801</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624290</v>
+        <v>129624216</v>
       </c>
       <c r="B30" t="n">
-        <v>100983</v>
+        <v>101890</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665221</v>
+        <v>665152</v>
       </c>
       <c r="R30" t="n">
-        <v>6703828</v>
+        <v>6703982</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129624236</v>
       </c>
       <c r="B2" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129624239</v>
       </c>
       <c r="B3" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129624237</v>
       </c>
       <c r="B4" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129624288</v>
       </c>
       <c r="B5" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624258</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>91375</v>
+        <v>100986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665281</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703851</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624229</v>
+        <v>129624258</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665157</v>
+        <v>665281</v>
       </c>
       <c r="R7" t="n">
-        <v>6703792</v>
+        <v>6703851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B8" t="n">
-        <v>100983</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B9" t="n">
-        <v>100983</v>
+        <v>98775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R9" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B10" t="n">
-        <v>98772</v>
+        <v>100986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R10" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1556,7 +1556,7 @@
         <v>129624253</v>
       </c>
       <c r="B11" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129624283</v>
       </c>
       <c r="B13" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129624234</v>
       </c>
       <c r="B14" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129624231</v>
       </c>
       <c r="B16" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129624252</v>
       </c>
       <c r="B17" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>129624238</v>
       </c>
       <c r="B18" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129624274</v>
       </c>
       <c r="B19" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129624286</v>
       </c>
       <c r="B20" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129624272</v>
       </c>
       <c r="B21" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129624291</v>
       </c>
       <c r="B22" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>129624271</v>
       </c>
       <c r="B23" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>129624289</v>
       </c>
       <c r="B24" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129624230</v>
       </c>
       <c r="B25" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129624268</v>
       </c>
       <c r="B26" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624290</v>
+        <v>129624224</v>
       </c>
       <c r="B27" t="n">
-        <v>100983</v>
+        <v>97043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665221</v>
+        <v>665142</v>
       </c>
       <c r="R27" t="n">
-        <v>6703828</v>
+        <v>6703804</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3252,6 +3252,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3268,32 +3283,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624224</v>
+        <v>129624240</v>
       </c>
       <c r="B28" t="n">
-        <v>97040</v>
+        <v>96143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665142</v>
+        <v>665198</v>
       </c>
       <c r="R28" t="n">
-        <v>6703804</v>
+        <v>6703801</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3349,21 +3364,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,10 +3380,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624240</v>
+        <v>129624216</v>
       </c>
       <c r="B29" t="n">
-        <v>96140</v>
+        <v>101893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3391,21 +3391,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2818</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665198</v>
+        <v>665152</v>
       </c>
       <c r="R29" t="n">
-        <v>6703801</v>
+        <v>6703982</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624216</v>
+        <v>129624290</v>
       </c>
       <c r="B30" t="n">
-        <v>101890</v>
+        <v>100986</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665152</v>
+        <v>665221</v>
       </c>
       <c r="R30" t="n">
-        <v>6703982</v>
+        <v>6703828</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3577,7 +3577,7 @@
         <v>129624267</v>
       </c>
       <c r="B31" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>129624295</v>
       </c>
       <c r="B34" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1063,45 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B6" t="n">
-        <v>100986</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,50 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>100986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R8" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B9" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R9" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B10" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R10" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B32" t="n">
-        <v>100986</v>
+        <v>91569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,6 +3744,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3752,6 +3757,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3768,10 +3788,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B33" t="n">
-        <v>91569</v>
+        <v>100986</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3799,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3823,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3861,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3869,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -1063,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624229</v>
+        <v>129624285</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>100986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665157</v>
+        <v>665187</v>
       </c>
       <c r="R6" t="n">
-        <v>6703792</v>
+        <v>6703837</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1262,45 +1257,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624285</v>
+        <v>129624229</v>
       </c>
       <c r="B8" t="n">
-        <v>100986</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665187</v>
+        <v>665157</v>
       </c>
       <c r="R8" t="n">
-        <v>6703837</v>
+        <v>6703792</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624287</v>
+        <v>129624254</v>
       </c>
       <c r="B9" t="n">
-        <v>100986</v>
+        <v>98775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665301</v>
+        <v>665212</v>
       </c>
       <c r="R9" t="n">
-        <v>6703874</v>
+        <v>6703814</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624254</v>
+        <v>129624287</v>
       </c>
       <c r="B10" t="n">
-        <v>98775</v>
+        <v>100986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665212</v>
+        <v>665301</v>
       </c>
       <c r="R10" t="n">
-        <v>6703814</v>
+        <v>6703874</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624225</v>
+        <v>129624284</v>
       </c>
       <c r="B32" t="n">
-        <v>91569</v>
+        <v>100986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665302</v>
+        <v>665177</v>
       </c>
       <c r="R32" t="n">
-        <v>6703887</v>
+        <v>6703824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3744,11 +3744,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3752,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3788,10 +3768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624284</v>
+        <v>129624225</v>
       </c>
       <c r="B33" t="n">
-        <v>100986</v>
+        <v>91569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,21 +3779,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3823,10 +3803,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665177</v>
+        <v>665302</v>
       </c>
       <c r="R33" t="n">
-        <v>6703824</v>
+        <v>6703887</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3861,6 +3841,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3869,6 +3854,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129624236</v>
+        <v>129624224</v>
       </c>
       <c r="B2" t="n">
-        <v>96143</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665196</v>
+        <v>665142</v>
       </c>
       <c r="R2" t="n">
-        <v>6703839</v>
+        <v>6703804</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129624239</v>
+        <v>129624271</v>
       </c>
       <c r="B3" t="n">
-        <v>96143</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665227</v>
+        <v>665238</v>
       </c>
       <c r="R3" t="n">
-        <v>6703829</v>
+        <v>6703837</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129624237</v>
+        <v>129624272</v>
       </c>
       <c r="B4" t="n">
-        <v>96143</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665235</v>
+        <v>665227</v>
       </c>
       <c r="R4" t="n">
-        <v>6703837</v>
+        <v>6703829</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129624288</v>
+        <v>129624273</v>
       </c>
       <c r="B5" t="n">
-        <v>100986</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665061</v>
+        <v>665207</v>
       </c>
       <c r="R5" t="n">
-        <v>6703834</v>
+        <v>6703784</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1039,6 +1054,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>dikad</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1047,6 +1067,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrsumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1063,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129624285</v>
+        <v>129624259</v>
       </c>
       <c r="B6" t="n">
-        <v>100986</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665187</v>
+        <v>665200</v>
       </c>
       <c r="R6" t="n">
-        <v>6703837</v>
+        <v>6703786</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1144,6 +1169,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1160,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129624258</v>
+        <v>129624231</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665281</v>
+        <v>665273</v>
       </c>
       <c r="R7" t="n">
-        <v>6703851</v>
+        <v>6703827</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,50 +1297,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129624229</v>
+        <v>129624232</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>96458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665157</v>
+        <v>665084</v>
       </c>
       <c r="R8" t="n">
-        <v>6703792</v>
+        <v>6703823</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129624254</v>
+        <v>129624233</v>
       </c>
       <c r="B9" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665212</v>
+        <v>665097</v>
       </c>
       <c r="R9" t="n">
-        <v>6703814</v>
+        <v>6703818</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1456,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129624287</v>
+        <v>129624234</v>
       </c>
       <c r="B10" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665301</v>
+        <v>665142</v>
       </c>
       <c r="R10" t="n">
-        <v>6703874</v>
+        <v>6703802</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1553,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129624253</v>
+        <v>129624235</v>
       </c>
       <c r="B11" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665178</v>
+        <v>665136</v>
       </c>
       <c r="R11" t="n">
-        <v>6703813</v>
+        <v>6703779</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129624281</v>
+        <v>129624236</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,39 +1696,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665191</v>
+        <v>665196</v>
       </c>
       <c r="R12" t="n">
-        <v>6703989</v>
+        <v>6703839</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1736,21 +1766,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1767,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129624283</v>
+        <v>129624237</v>
       </c>
       <c r="B13" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665302</v>
+        <v>665235</v>
       </c>
       <c r="R13" t="n">
-        <v>6703853</v>
+        <v>6703837</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1864,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129624234</v>
+        <v>129624238</v>
       </c>
       <c r="B14" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665142</v>
+        <v>665241</v>
       </c>
       <c r="R14" t="n">
-        <v>6703802</v>
+        <v>6703839</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1961,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129624282</v>
+        <v>129624239</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,39 +1987,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665066</v>
+        <v>665227</v>
       </c>
       <c r="R15" t="n">
-        <v>6703824</v>
+        <v>6703829</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2047,21 +2057,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2078,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129624231</v>
+        <v>129624240</v>
       </c>
       <c r="B16" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665273</v>
+        <v>665198</v>
       </c>
       <c r="R16" t="n">
-        <v>6703827</v>
+        <v>6703801</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,10 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129624252</v>
+        <v>129624241</v>
       </c>
       <c r="B17" t="n">
-        <v>98775</v>
+        <v>96458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,21 +2181,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665269</v>
+        <v>665201</v>
       </c>
       <c r="R17" t="n">
-        <v>6703827</v>
+        <v>6703797</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2272,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129624238</v>
+        <v>129624242</v>
       </c>
       <c r="B18" t="n">
-        <v>96143</v>
+        <v>96458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665241</v>
+        <v>665207</v>
       </c>
       <c r="R18" t="n">
-        <v>6703839</v>
+        <v>6703784</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2369,30 +2364,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129624274</v>
+        <v>129624243</v>
       </c>
       <c r="B19" t="n">
-        <v>91625</v>
+        <v>96458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2400,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665304</v>
+        <v>665200</v>
       </c>
       <c r="R19" t="n">
-        <v>6703880</v>
+        <v>6703771</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2446,21 +2445,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2477,10 +2461,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129624286</v>
+        <v>129624244</v>
       </c>
       <c r="B20" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2472,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2496,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665264</v>
+        <v>665182</v>
       </c>
       <c r="R20" t="n">
-        <v>6703843</v>
+        <v>6703749</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2574,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129624272</v>
+        <v>129624258</v>
       </c>
       <c r="B21" t="n">
-        <v>96239</v>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2569,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2609,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665227</v>
+        <v>665281</v>
       </c>
       <c r="R21" t="n">
-        <v>6703829</v>
+        <v>6703851</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2671,10 +2655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129624291</v>
+        <v>129624230</v>
       </c>
       <c r="B22" t="n">
-        <v>100986</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2666,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2709,7 +2693,7 @@
         <v>665217</v>
       </c>
       <c r="R22" t="n">
-        <v>6703817</v>
+        <v>6703818</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2768,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129624271</v>
+        <v>129624225</v>
       </c>
       <c r="B23" t="n">
-        <v>96239</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2779,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665238</v>
+        <v>665302</v>
       </c>
       <c r="R23" t="n">
-        <v>6703837</v>
+        <v>6703887</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2841,6 +2825,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På död gren</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2849,6 +2838,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2865,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129624289</v>
+        <v>129624267</v>
       </c>
       <c r="B24" t="n">
-        <v>100986</v>
+        <v>75428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2900,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665153</v>
+        <v>665294</v>
       </c>
       <c r="R24" t="n">
-        <v>6703824</v>
+        <v>6703872</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2962,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129624230</v>
+        <v>129624268</v>
       </c>
       <c r="B25" t="n">
-        <v>92560</v>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665217</v>
+        <v>665254</v>
       </c>
       <c r="R25" t="n">
-        <v>6703818</v>
+        <v>6703848</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3043,6 +3047,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3059,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129624268</v>
+        <v>129624246</v>
       </c>
       <c r="B26" t="n">
-        <v>75199</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3089,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665254</v>
+        <v>665142</v>
       </c>
       <c r="R26" t="n">
-        <v>6703848</v>
+        <v>6703786</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3140,21 +3164,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3171,45 +3180,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129624224</v>
+        <v>129624281</v>
       </c>
       <c r="B27" t="n">
-        <v>97043</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665142</v>
+        <v>665191</v>
       </c>
       <c r="R27" t="n">
-        <v>6703804</v>
+        <v>6703989</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3255,17 +3269,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3283,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129624240</v>
+        <v>129624282</v>
       </c>
       <c r="B28" t="n">
-        <v>96143</v>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,34 +3308,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665198</v>
+        <v>665066</v>
       </c>
       <c r="R28" t="n">
-        <v>6703801</v>
+        <v>6703824</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3364,6 +3383,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3380,45 +3414,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129624216</v>
+        <v>129624229</v>
       </c>
       <c r="B29" t="n">
-        <v>101893</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Olarsbo, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665152</v>
+        <v>665157</v>
       </c>
       <c r="R29" t="n">
-        <v>6703982</v>
+        <v>6703792</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3477,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624290</v>
+        <v>129624252</v>
       </c>
       <c r="B30" t="n">
-        <v>100986</v>
+        <v>99096</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3512,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665221</v>
+        <v>665269</v>
       </c>
       <c r="R30" t="n">
-        <v>6703828</v>
+        <v>6703827</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3574,10 +3613,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129624267</v>
+        <v>129624253</v>
       </c>
       <c r="B31" t="n">
-        <v>75199</v>
+        <v>99096</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3585,21 +3624,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3609,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665294</v>
+        <v>665178</v>
       </c>
       <c r="R31" t="n">
-        <v>6703872</v>
+        <v>6703813</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3671,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129624284</v>
+        <v>129624254</v>
       </c>
       <c r="B32" t="n">
-        <v>100986</v>
+        <v>99096</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3706,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665177</v>
+        <v>665212</v>
       </c>
       <c r="R32" t="n">
-        <v>6703824</v>
+        <v>6703814</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3768,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129624225</v>
+        <v>129624255</v>
       </c>
       <c r="B33" t="n">
-        <v>91569</v>
+        <v>99096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3803,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665302</v>
+        <v>665198</v>
       </c>
       <c r="R33" t="n">
-        <v>6703887</v>
+        <v>6703797</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3841,11 +3880,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På död gren</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3854,21 +3888,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3885,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129624295</v>
+        <v>129624257</v>
       </c>
       <c r="B34" t="n">
-        <v>106425</v>
+        <v>99096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3920,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665247</v>
+        <v>665178</v>
       </c>
       <c r="R34" t="n">
-        <v>6703823</v>
+        <v>6703755</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3979,6 +3998,1267 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129624295</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>665247</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703823</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129624216</v>
+      </c>
+      <c r="B36" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>665152</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703982</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129624283</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>665302</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703853</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129624284</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>665177</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703824</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129624285</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>665187</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6703837</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129624286</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>665264</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6703843</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129624287</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>665301</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6703874</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129624288</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>665061</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6703834</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129624289</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>665153</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6703824</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129624290</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>665221</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6703828</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129624291</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>665217</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6703817</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129624292</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>665198</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6703797</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129624293</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Olarsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>665200</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6703770</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49882-2025 artfynd.xlsx
+++ b/artfynd/A 49882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624273</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624231</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624232</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624233</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624234</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624235</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624236</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624237</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624238</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624239</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624240</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624241</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624242</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624243</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624244</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624258</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,6 +2854,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624230</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624225</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624267</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,6 +3195,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624268</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,6 +3302,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624246</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3294,6 +3424,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624281</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3411,6 +3546,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3513,6 +3653,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624229</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3610,6 +3755,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624252</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3707,6 +3857,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624253</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3804,6 +3959,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624254</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3901,6 +4061,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624255</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3998,6 +4163,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624257</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4095,6 +4265,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624295</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4192,6 +4367,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624216</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4289,6 +4469,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624283</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4386,6 +4571,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624284</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4483,6 +4673,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624285</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4580,6 +4775,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624286</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4677,6 +4877,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624287</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4774,6 +4979,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624288</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4871,6 +5081,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624289</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4968,6 +5183,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624290</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5065,6 +5285,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624291</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5162,6 +5387,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624292</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5259,8 +5489,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624293</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>